--- a/backend/data/financials_by_company/0979.HK.xlsx
+++ b/backend/data/financials_by_company/0979.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>1158135</v>
+        <v>-260535</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-7622000</v>
+        <v>-20820000</v>
       </c>
       <c r="E2" t="n">
-        <v>7019000</v>
+        <v>-1579000</v>
       </c>
       <c r="F2" t="n">
-        <v>7019000</v>
+        <v>-1579000</v>
       </c>
       <c r="G2" t="n">
-        <v>-4207000</v>
+        <v>-21165000</v>
       </c>
       <c r="H2" t="n">
-        <v>4110000</v>
+        <v>3700000</v>
       </c>
       <c r="I2" t="n">
-        <v>60823000</v>
+        <v>49273000</v>
       </c>
       <c r="J2" t="n">
-        <v>-603000</v>
+        <v>-22399000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4713000</v>
+        <v>-26099000</v>
       </c>
       <c r="L2" t="n">
-        <v>183000</v>
+        <v>545000</v>
       </c>
       <c r="M2" t="n">
-        <v>134000</v>
+        <v>91000</v>
       </c>
       <c r="N2" t="n">
-        <v>317000</v>
+        <v>636000</v>
       </c>
       <c r="O2" t="n">
-        <v>-10067865</v>
+        <v>-19846535</v>
       </c>
       <c r="P2" t="n">
-        <v>-9034000</v>
+        <v>-21165000</v>
       </c>
       <c r="Q2" t="n">
-        <v>92784000</v>
+        <v>88502000</v>
       </c>
       <c r="R2" t="n">
         <v>1136308000</v>
@@ -719,89 +719,87 @@
         <v>1136308000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0186</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0186</v>
       </c>
       <c r="V2" t="n">
-        <v>-9034000</v>
+        <v>-21165000</v>
       </c>
       <c r="W2" t="n">
-        <v>-9034000</v>
+        <v>-21165000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-9034000</v>
+        <v>-21165000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1022000</v>
+        <v>5043000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-10056000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-4827000</v>
-      </c>
+        <v>-26208000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-5229000</v>
+        <v>-26208000</v>
       </c>
       <c r="AD2" t="n">
-        <v>382000</v>
+        <v>18000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4847000</v>
+        <v>-26190000</v>
       </c>
       <c r="AF2" t="n">
-        <v>980000</v>
+        <v>460000</v>
       </c>
       <c r="AG2" t="n">
-        <v>7019000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-7367000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-1579000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>1579000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>348000</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>183000</v>
+        <v>545000</v>
       </c>
       <c r="AL2" t="n">
-        <v>134000</v>
+        <v>91000</v>
       </c>
       <c r="AM2" t="n">
-        <v>317000</v>
+        <v>636000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-12924000</v>
+        <v>-28236000</v>
       </c>
       <c r="AO2" t="n">
-        <v>31961000</v>
+        <v>39229000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11831000</v>
+        <v>20234000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3353000</v>
+        <v>3600000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3353000</v>
+        <v>3600000</v>
       </c>
       <c r="AS2" t="n">
-        <v>19037000</v>
+        <v>10993000</v>
       </c>
       <c r="AT2" t="n">
-        <v>60823000</v>
+        <v>49273000</v>
       </c>
       <c r="AU2" t="n">
-        <v>79860000</v>
+        <v>60266000</v>
       </c>
       <c r="AV2" t="n">
-        <v>79860000</v>
+        <v>60266000</v>
       </c>
     </row>
     <row r="3">
@@ -952,55 +950,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-260535</v>
+        <v>1158135</v>
       </c>
       <c r="C4" t="n">
         <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>-20820000</v>
+        <v>-7622000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1579000</v>
+        <v>7019000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1579000</v>
+        <v>7019000</v>
       </c>
       <c r="G4" t="n">
-        <v>-21165000</v>
+        <v>-4207000</v>
       </c>
       <c r="H4" t="n">
-        <v>3700000</v>
+        <v>4110000</v>
       </c>
       <c r="I4" t="n">
-        <v>49273000</v>
+        <v>60823000</v>
       </c>
       <c r="J4" t="n">
-        <v>-22399000</v>
+        <v>-603000</v>
       </c>
       <c r="K4" t="n">
-        <v>-26099000</v>
+        <v>-4713000</v>
       </c>
       <c r="L4" t="n">
-        <v>545000</v>
+        <v>183000</v>
       </c>
       <c r="M4" t="n">
-        <v>91000</v>
+        <v>134000</v>
       </c>
       <c r="N4" t="n">
-        <v>636000</v>
+        <v>317000</v>
       </c>
       <c r="O4" t="n">
-        <v>-19846535</v>
+        <v>-10067865</v>
       </c>
       <c r="P4" t="n">
-        <v>-21165000</v>
+        <v>-9034000</v>
       </c>
       <c r="Q4" t="n">
-        <v>88502000</v>
+        <v>92784000</v>
       </c>
       <c r="R4" t="n">
         <v>1136308000</v>
@@ -1009,87 +1007,89 @@
         <v>1136308000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0186</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0186</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-21165000</v>
+        <v>-9034000</v>
       </c>
       <c r="W4" t="n">
-        <v>-21165000</v>
+        <v>-9034000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-21165000</v>
+        <v>-9034000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5043000</v>
+        <v>1022000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-26208000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>-10056000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-4827000</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-26208000</v>
+        <v>-5229000</v>
       </c>
       <c r="AD4" t="n">
-        <v>18000</v>
+        <v>382000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-26190000</v>
+        <v>-4847000</v>
       </c>
       <c r="AF4" t="n">
-        <v>460000</v>
+        <v>980000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1579000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>1579000</v>
-      </c>
+        <v>7019000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-7367000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>348000</v>
       </c>
       <c r="AK4" t="n">
-        <v>545000</v>
+        <v>183000</v>
       </c>
       <c r="AL4" t="n">
-        <v>91000</v>
+        <v>134000</v>
       </c>
       <c r="AM4" t="n">
-        <v>636000</v>
+        <v>317000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-28236000</v>
+        <v>-12924000</v>
       </c>
       <c r="AO4" t="n">
-        <v>39229000</v>
+        <v>31961000</v>
       </c>
       <c r="AP4" t="n">
-        <v>20234000</v>
+        <v>11831000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3600000</v>
+        <v>3353000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3600000</v>
+        <v>3353000</v>
       </c>
       <c r="AS4" t="n">
-        <v>10993000</v>
+        <v>19037000</v>
       </c>
       <c r="AT4" t="n">
-        <v>49273000</v>
+        <v>60823000</v>
       </c>
       <c r="AU4" t="n">
-        <v>60266000</v>
+        <v>79860000</v>
       </c>
       <c r="AV4" t="n">
-        <v>60266000</v>
+        <v>79860000</v>
       </c>
     </row>
   </sheetData>
@@ -1370,49 +1370,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>1136308176</v>
+        <v>1136308000</v>
       </c>
       <c r="C2" t="n">
-        <v>1136308176</v>
+        <v>1136308000</v>
       </c>
       <c r="D2" t="n">
-        <v>5726000</v>
+        <v>905000</v>
       </c>
       <c r="E2" t="n">
-        <v>41387000</v>
+        <v>80695000</v>
       </c>
       <c r="F2" t="n">
-        <v>41387000</v>
+        <v>80873000</v>
       </c>
       <c r="G2" t="n">
-        <v>17671000</v>
+        <v>43992000</v>
       </c>
       <c r="H2" t="n">
-        <v>41387000</v>
+        <v>80695000</v>
       </c>
       <c r="I2" t="n">
-        <v>5726000</v>
+        <v>905000</v>
       </c>
       <c r="J2" t="n">
-        <v>41387000</v>
+        <v>80873000</v>
       </c>
       <c r="K2" t="n">
-        <v>41387000</v>
+        <v>80873000</v>
       </c>
       <c r="L2" t="n">
-        <v>38441000</v>
+        <v>77894000</v>
       </c>
       <c r="M2" t="n">
-        <v>-2946000</v>
+        <v>-2979000</v>
       </c>
       <c r="N2" t="n">
-        <v>41387000</v>
+        <v>80873000</v>
       </c>
       <c r="O2" t="n">
-        <v>-548485000</v>
+        <v>-511720000</v>
       </c>
       <c r="P2" t="n">
         <v>471908000</v>
@@ -1424,104 +1424,108 @@
         <v>113631000</v>
       </c>
       <c r="S2" t="n">
-        <v>12246000</v>
+        <v>12314000</v>
       </c>
       <c r="T2" t="n">
-        <v>3787000</v>
+        <v>237000</v>
       </c>
       <c r="U2" t="n">
-        <v>3787000</v>
+        <v>237000</v>
       </c>
       <c r="V2" t="n">
-        <v>3787000</v>
+        <v>237000</v>
       </c>
       <c r="W2" t="n">
-        <v>8459000</v>
+        <v>12077000</v>
       </c>
       <c r="X2" t="n">
-        <v>1939000</v>
+        <v>668000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1939000</v>
+        <v>668000</v>
       </c>
       <c r="Z2" t="n">
-        <v>4194000</v>
+        <v>6599000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3713000</v>
+        <v>6285000</v>
       </c>
       <c r="AB2" t="n">
-        <v>370000</v>
+        <v>2000</v>
       </c>
       <c r="AC2" t="n">
-        <v>111000</v>
+        <v>312000</v>
       </c>
       <c r="AD2" t="n">
-        <v>50687000</v>
+        <v>90208000</v>
       </c>
       <c r="AE2" t="n">
-        <v>24557000</v>
+        <v>34139000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1764000</v>
+        <v>1072000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>178000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>178000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>22793000</v>
+        <v>32889000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-17796000</v>
+        <v>-21546000</v>
       </c>
       <c r="AK2" t="n">
-        <v>40589000</v>
+        <v>54435000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5673000</v>
+        <v>890000</v>
       </c>
       <c r="AM2" t="n">
-        <v>19139000</v>
+        <v>28973000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4565000</v>
+        <v>6794000</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>26130000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>56069000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10888000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>1221000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>1340000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>933000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>1221000</v>
+        <v>1340000</v>
       </c>
       <c r="AU2" t="n">
-        <v>7273000</v>
+        <v>10888000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2787000</v>
+        <v>3617000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>-1531000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2787000</v>
+        <v>5148000</v>
       </c>
       <c r="AY2" t="n">
-        <v>14849000</v>
+        <v>40224000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14849000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>14849000</v>
-      </c>
+        <v>40224000</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1684,49 +1688,49 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>1136308000</v>
+        <v>1136308176</v>
       </c>
       <c r="C4" t="n">
-        <v>1136308000</v>
+        <v>1136308176</v>
       </c>
       <c r="D4" t="n">
-        <v>905000</v>
+        <v>5726000</v>
       </c>
       <c r="E4" t="n">
-        <v>80695000</v>
+        <v>41387000</v>
       </c>
       <c r="F4" t="n">
-        <v>80873000</v>
+        <v>41387000</v>
       </c>
       <c r="G4" t="n">
-        <v>43992000</v>
+        <v>17671000</v>
       </c>
       <c r="H4" t="n">
-        <v>80695000</v>
+        <v>41387000</v>
       </c>
       <c r="I4" t="n">
-        <v>905000</v>
+        <v>5726000</v>
       </c>
       <c r="J4" t="n">
-        <v>80873000</v>
+        <v>41387000</v>
       </c>
       <c r="K4" t="n">
-        <v>80873000</v>
+        <v>41387000</v>
       </c>
       <c r="L4" t="n">
-        <v>77894000</v>
+        <v>38441000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2979000</v>
+        <v>-2946000</v>
       </c>
       <c r="N4" t="n">
-        <v>80873000</v>
+        <v>41387000</v>
       </c>
       <c r="O4" t="n">
-        <v>-511720000</v>
+        <v>-548485000</v>
       </c>
       <c r="P4" t="n">
         <v>471908000</v>
@@ -1738,108 +1742,104 @@
         <v>113631000</v>
       </c>
       <c r="S4" t="n">
-        <v>12314000</v>
+        <v>12246000</v>
       </c>
       <c r="T4" t="n">
-        <v>237000</v>
+        <v>3787000</v>
       </c>
       <c r="U4" t="n">
-        <v>237000</v>
+        <v>3787000</v>
       </c>
       <c r="V4" t="n">
-        <v>237000</v>
+        <v>3787000</v>
       </c>
       <c r="W4" t="n">
-        <v>12077000</v>
+        <v>8459000</v>
       </c>
       <c r="X4" t="n">
-        <v>668000</v>
+        <v>1939000</v>
       </c>
       <c r="Y4" t="n">
-        <v>668000</v>
+        <v>1939000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6599000</v>
+        <v>4194000</v>
       </c>
       <c r="AA4" t="n">
-        <v>6285000</v>
+        <v>3713000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2000</v>
+        <v>370000</v>
       </c>
       <c r="AC4" t="n">
-        <v>312000</v>
+        <v>111000</v>
       </c>
       <c r="AD4" t="n">
-        <v>90208000</v>
+        <v>50687000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34139000</v>
+        <v>24557000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1072000</v>
+        <v>1764000</v>
       </c>
       <c r="AG4" t="n">
-        <v>178000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>178000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>32889000</v>
+        <v>22793000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-21546000</v>
+        <v>-17796000</v>
       </c>
       <c r="AK4" t="n">
-        <v>54435000</v>
+        <v>40589000</v>
       </c>
       <c r="AL4" t="n">
-        <v>890000</v>
+        <v>5673000</v>
       </c>
       <c r="AM4" t="n">
-        <v>28973000</v>
+        <v>19139000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6794000</v>
+        <v>4565000</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>56069000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10888000</v>
-      </c>
+        <v>26130000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>933000</v>
-      </c>
+        <v>1221000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1340000</v>
+        <v>1221000</v>
       </c>
       <c r="AU4" t="n">
-        <v>10888000</v>
+        <v>7273000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3617000</v>
+        <v>2787000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1531000</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>5148000</v>
+        <v>2787000</v>
       </c>
       <c r="AY4" t="n">
-        <v>40224000</v>
+        <v>14849000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>40224000</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
+        <v>14849000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14849000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2039,105 +2039,113 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45107</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-16479000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-30003000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
-        <v>-34000</v>
+        <v>-4873000</v>
       </c>
       <c r="E2" t="n">
-        <v>14849000</v>
+        <v>40224000</v>
       </c>
       <c r="F2" t="n">
-        <v>33566000</v>
+        <v>70133000</v>
       </c>
       <c r="G2" t="n">
-        <v>-849000</v>
+        <v>-547000</v>
       </c>
       <c r="H2" t="n">
-        <v>-17868000</v>
+        <v>-29362000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1480000</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>5000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1400000</v>
+      </c>
       <c r="K2" t="n">
-        <v>-136000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>-91000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>57000</v>
+        <v>-4237000</v>
       </c>
       <c r="O2" t="n">
-        <v>151000</v>
+        <v>636000</v>
       </c>
       <c r="P2" t="n">
-        <v>-60000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
-        <v>-60000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-34000</v>
+        <v>-4873000</v>
       </c>
       <c r="T2" t="n">
-        <v>-34000</v>
+        <v>-4873000</v>
       </c>
       <c r="U2" t="n">
-        <v>-16445000</v>
+        <v>-25130000</v>
       </c>
       <c r="V2" t="n">
-        <v>-12000</v>
+        <v>-22000</v>
       </c>
       <c r="W2" t="n">
-        <v>-3864000</v>
+        <v>-3657000</v>
       </c>
       <c r="X2" t="n">
-        <v>-4475000</v>
+        <v>58000</v>
       </c>
       <c r="Y2" t="n">
-        <v>3224000</v>
+        <v>4546000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2654000</v>
+        <v>-142000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1888000</v>
+        <v>-6852000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6000</v>
+        <v>-380000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1853000</v>
+        <v>-887000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-181000</v>
+        <v>-545000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4110000</v>
+        <v>3700000</v>
       </c>
       <c r="AF2" t="n">
-        <v>78000</v>
+        <v>100000</v>
       </c>
       <c r="AG2" t="n">
-        <v>4032000</v>
+        <v>3600000</v>
       </c>
       <c r="AH2" t="n">
+        <v>-62000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="n">
-        <v>-1007000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-6360000</v>
-      </c>
       <c r="AK2" t="n">
-        <v>-9674000</v>
+        <v>-26190000</v>
       </c>
     </row>
     <row r="3">
@@ -2245,113 +2253,105 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44377</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-30003000</v>
-      </c>
-      <c r="C4" t="n">
+        <v>-16479000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14849000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>33566000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-849000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-17868000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1480000</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>-136000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>151000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-16445000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-3864000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-4475000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3224000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-2654000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1888000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1853000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-181000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4110000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>78000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4032000</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>-4873000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>40224000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>70133000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-547000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-29362000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-91000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-4237000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>636000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-4873000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-4873000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-25130000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-22000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-3657000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>58000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4546000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-142000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-6852000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-380000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-887000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-545000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-62000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>-1007000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-6360000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-26190000</v>
+        <v>-9674000</v>
       </c>
     </row>
   </sheetData>
@@ -2876,187 +2876,187 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3159,58 +3159,58 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0.305</v>
+        <v>0.45</v>
       </c>
       <c r="W2" t="n">
-        <v>0.305</v>
+        <v>0.345</v>
       </c>
       <c r="X2" t="n">
-        <v>0.305</v>
+        <v>0.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.305</v>
+        <v>0.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.305</v>
+        <v>0.345</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.305</v>
+        <v>0.45</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.861</v>
+        <v>0.897</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.95312506</v>
+        <v>0.948718</v>
       </c>
       <c r="AF2" t="n">
-        <v>60000</v>
+        <v>1240000</v>
       </c>
       <c r="AG2" t="n">
-        <v>60000</v>
+        <v>1240000</v>
       </c>
       <c r="AH2" t="n">
-        <v>489139</v>
+        <v>483545</v>
       </c>
       <c r="AI2" t="n">
-        <v>271111</v>
+        <v>416480</v>
       </c>
       <c r="AJ2" t="n">
-        <v>271111</v>
+        <v>416480</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.295</v>
+        <v>0.345</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.305</v>
+        <v>0.405</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>413674016</v>
+        <v>501834048</v>
       </c>
       <c r="AP2" t="n">
         <v>379766289</v>
@@ -3237,13 +3237,13 @@
         <v>0.057</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.374022</v>
+        <v>7.73242</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2811</v>
+        <v>0.2999</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.289895</v>
+        <v>0.29462</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>403744992</v>
+        <v>491905024</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.21239</v>
@@ -3284,7 +3284,7 @@
         <v>0.026</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.730769</v>
+        <v>14.230769</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -3299,22 +3299,22 @@
         <v>-13778000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="BP2" t="n">
         <v>0.85</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.221</v>
+        <v>7.579</v>
       </c>
       <c r="BR2" t="n">
-        <v>-27.715</v>
+        <v>-33.766</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.25</v>
+        <v>0.42857146</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.305</v>
+        <v>0.37</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -3421,140 +3421,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>1.6666651</v>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Green Energy Group Limited</t>
+        </is>
       </c>
       <c r="CY2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+        <v>5.7142887</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
         <is>
           <t>GREEN ENERGY GP</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1127957400000</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.02000001</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>0.345 - 0.45</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1782114938</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>finmb_4508997</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DE2" t="n">
+      <c r="DM2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DG2" t="b">
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780381397</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Green Energy Group Limited</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
+      <c r="DP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DM2" t="n">
-        <v>0.004999995</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0.305 - 0.305</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DP2" t="n">
-        <v>489139</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.12400001</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.685083</v>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>483545</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.18900001</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1.044199</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>0.181 - 0.46</t>
         </is>
       </c>
-      <c r="DT2" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.33695653</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>25</v>
-      </c>
-      <c r="DW2" t="n">
+      <c r="DX2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.19565217</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>42.857147</v>
+      </c>
+      <c r="EA2" t="n">
         <v>1740653940</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EB2" t="n">
         <v>1740653940</v>
       </c>
-      <c r="DY2" t="b">
+      <c r="EC2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.023900002</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.08502313</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.015105009</v>
-      </c>
       <c r="ED2" t="n">
-        <v>0.052105103</v>
+        <v>0.39</v>
       </c>
       <c r="EE2" t="n">
-        <v>15</v>
+        <v>0.07010001</v>
       </c>
       <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
+        <v>0.23374462</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.07538</v>
       </c>
       <c r="EH2" t="n">
-        <v>1127957400000</v>
+        <v>0.255855</v>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
